--- a/site/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Match Expression</t>
+          <t>Source Filter Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KFZEGGV68F71BB72KC3GH9F4</t>
+          <t>h_01KHK3JKV34Y0D32P0Y4F91316</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KFZEGGV68F71BB72KC3GH9F4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KHK3JKV34Y0D32P0Y4F91316</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Contractor Creation Settings</t>
+          <t>Match Expression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KFZEHYZWX84H2VQ9DAJ8XQ7W</t>
+          <t>h_01KFZEGGV68F71BB72KC3GH9F4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KFZEHYZWX84H2VQ9DAJ8XQ7W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KFZEGGV68F71BB72KC3GH9F4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Manage End Date</t>
+          <t>Contractor Creation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KC6HYWY0APQ3BRAS1FXAEQK6</t>
+          <t>h_01KFZEHYZWX84H2VQ9DAJ8XQ7W</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6HYWY0APQ3BRAS1FXAEQK6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KFZEHYZWX84H2VQ9DAJ8XQ7W</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Manage End Date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
+          <t>h_01KC6HYWY0APQ3BRAS1FXAEQK6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6HYWY0APQ3BRAS1FXAEQK6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,151 +781,151 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KC6J2N08947K00S859KHW0PV</t>
+          <t>h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6J2N08947K00S859KHW0PV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KC6J2N08947K00S859KHW0PV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6J2N08947K00S859KHW0PV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Contractor Naming Policy</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KC61HN1T7APW85CMB7R1HRRM</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC61HN1T7APW85CMB7R1HRRM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Naming Policy Settings</t>
+          <t>Contractor Naming Policy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KC61MFYNGXQ0TKK3EJ443G16</t>
+          <t>h_01KC61HN1T7APW85CMB7R1HRRM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC61MFYNGXQ0TKK3EJ443G16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC61HN1T7APW85CMB7R1HRRM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Contractor Password Policy</t>
+          <t>Naming Policy Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KC6BVBDVTRAAN3EFX130CVVW</t>
+          <t>h_01KC61MFYNGXQ0TKK3EJ443G16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6BVBDVTRAAN3EFX130CVVW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC61MFYNGXQ0TKK3EJ443G16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Contractor Password Policy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KC8N0H76EWR3JBVXRFPB18KZ</t>
+          <t>h_01KC6BVBDVTRAAN3EFX130CVVW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC8N0H76EWR3JBVXRFPB18KZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6BVBDVTRAAN3EFX130CVVW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
+          <t>h_01KC8N0H76EWR3JBVXRFPB18KZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC8N0H76EWR3JBVXRFPB18KZ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KC6HD3EB177Y4AE6GFEJQPEW</t>
+          <t>01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6HD3EB177Y4AE6GFEJQPEW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KC6HHSMA0FQQRJ7C15ASJ2EK</t>
+          <t>h_01KC6HD3EB177Y4AE6GFEJQPEW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6HHSMA0FQQRJ7C15ASJ2EK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6HD3EB177Y4AE6GFEJQPEW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KC8N0H76M1RZ12RH0654ADZQ</t>
+          <t>h_01KC6HHSMA0FQQRJ7C15ASJ2EK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC8N0H76M1RZ12RH0654ADZQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC6HHSMA0FQQRJ7C15ASJ2EK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KC8N0H76M1RZ12RH0654ADZQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC8N0H76M1RZ12RH0654ADZQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,54 +1023,76 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KC8N0H76E09222N9K6SS7PCP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC8N0H76E09222N9K6SS7PCP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KC8N0H76E09222N9K6SS7PCP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01KC8N0H76E09222N9K6SS7PCP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-to-Okta-Contractor-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
